--- a/data/trans_camb/P16A_n_R3-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R3-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 3,26</t>
+          <t>-0,35; 3,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 3,56</t>
+          <t>0,03; 3,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 12,38</t>
+          <t>6,86; 12,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,96</t>
+          <t>3,55; 7,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,32</t>
+          <t>2,81; 7,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,67; 23,29</t>
+          <t>17,14; 23,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,4</t>
+          <t>2,57; 5,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,17</t>
+          <t>2,18; 5,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,0; 17,98</t>
+          <t>14,07; 17,97</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 136,68</t>
+          <t>-15,73; 117,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 149,27</t>
+          <t>-0,25; 151,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167,91; 505,74</t>
+          <t>171,57; 515,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64,34; 189,71</t>
+          <t>57,66; 190,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,63; 180,36</t>
+          <t>47,37; 182,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>298,53; 570,35</t>
+          <t>281,43; 559,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,32; 154,6</t>
+          <t>55,2; 150,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,8; 146,77</t>
+          <t>47,71; 147,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>295,44; 511,73</t>
+          <t>290,78; 510,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,47</t>
+          <t>-0,62; 0,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,56</t>
+          <t>-0,52; 0,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,57</t>
+          <t>1,59; 3,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,82</t>
+          <t>-0,79; 0,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,78</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,99</t>
+          <t>2,3; 4,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,51</t>
+          <t>-0,53; 0,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 0,98</t>
+          <t>-0,08; 0,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,99</t>
+          <t>2,27; 3,98</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-64,07; 111,44</t>
+          <t>-62,85; 149,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,96; 134,05</t>
+          <t>-55,87; 195,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141,15; 828,57</t>
+          <t>152,47; 816,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,52; 84,31</t>
+          <t>-43,67; 91,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 187,66</t>
+          <t>-1,23; 192,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>127,58; 510,25</t>
+          <t>135,15; 489,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,77; 65,22</t>
+          <t>-40,48; 57,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 123,88</t>
+          <t>-7,43; 123,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>187,25; 535,07</t>
+          <t>184,97; 519,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,37</t>
+          <t>-0,82; 2,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,8</t>
+          <t>-1,16; 0,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,72</t>
+          <t>0,19; 2,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,56</t>
+          <t>0,54; 3,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,62</t>
+          <t>0,34; 2,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,85</t>
+          <t>2,28; 4,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,42</t>
+          <t>0,09; 2,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,44</t>
+          <t>-0,3; 1,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,32</t>
+          <t>1,55; 3,29</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 569,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 265,63</t>
+          <t>-100,0; 426,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 679,28</t>
+          <t>-3,42; 927,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 751,53</t>
+          <t>-8,24; 718,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,43; 608,98</t>
+          <t>-46,68; 492,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>130,2; 1259,84</t>
+          <t>142,51; 1271,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,05</t>
+          <t>-0,32; 0,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,73</t>
+          <t>-0,41; 0,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,85</t>
+          <t>2,03; 3,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,35</t>
+          <t>1,58; 3,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,6</t>
+          <t>0,85; 2,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,66</t>
+          <t>4,77; 7,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,96</t>
+          <t>0,82; 2,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,51</t>
+          <t>0,43; 1,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,55</t>
+          <t>3,8; 5,56</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 83,64</t>
+          <t>-19,03; 82,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,01; 59,2</t>
+          <t>-25,2; 66,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>113,69; 318,24</t>
+          <t>115,26; 338,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53,72; 152,7</t>
+          <t>52,66; 155,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,84; 117,92</t>
+          <t>28,04; 114,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>171,13; 357,54</t>
+          <t>171,73; 346,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,86; 107,94</t>
+          <t>32,82; 107,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,05; 85,8</t>
+          <t>18,39; 86,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>171,93; 305,85</t>
+          <t>172,95; 309,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A_n_R3-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R3-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,55</t>
+          <t>8,95</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>19,64</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15,95</t>
+          <t>15,27</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 3,05</t>
+          <t>-0,45; 3,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,68</t>
+          <t>0,2; 3,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 12,17</t>
+          <t>6,54; 11,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,76</t>
+          <t>3,76; 8,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,64</t>
+          <t>2,74; 7,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,14; 23,05</t>
+          <t>17,12; 22,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,41</t>
+          <t>2,61; 5,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,17</t>
+          <t>2,16; 5,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 17,97</t>
+          <t>13,23; 17,26</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>307,03%</t>
+          <t>287,78%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>415,1%</t>
+          <t>403,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>389,41%</t>
+          <t>372,9%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 117,39</t>
+          <t>-13,64; 133,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 151,06</t>
+          <t>4,25; 174,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>171,57; 515,09</t>
+          <t>163,4; 509,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57,66; 190,86</t>
+          <t>65,11; 207,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,37; 182,54</t>
+          <t>48,74; 186,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>281,43; 559,42</t>
+          <t>293,08; 575,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,2; 150,79</t>
+          <t>53,45; 147,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,71; 147,18</t>
+          <t>43,93; 143,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>290,78; 510,8</t>
+          <t>267,23; 478,82</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>4,45</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,22</t>
+          <t>3,67</t>
         </is>
       </c>
     </row>
@@ -898,42 +898,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,62</t>
+          <t>-0,57; 0,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,6</t>
+          <t>2,02; 3,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,86</t>
+          <t>-0,79; 0,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>-0,03; 1,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,87</t>
+          <t>3,5; 5,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,45</t>
+          <t>-0,47; 0,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,98</t>
+          <t>-0,03; 0,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,98</t>
+          <t>3,09; 4,34</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>388,47%</t>
+          <t>426,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>274,94%</t>
+          <t>323,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>316,14%</t>
+          <t>361,11%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,85; 149,67</t>
+          <t>-64,42; 132,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,87; 195,41</t>
+          <t>-56,52; 151,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152,47; 816,85</t>
+          <t>158,89; 878,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,67; 91,85</t>
+          <t>-43,86; 98,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 192,32</t>
+          <t>-2,77; 180,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>135,15; 489,3</t>
+          <t>167,92; 585,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,48; 57,02</t>
+          <t>-39,38; 62,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 123,74</t>
+          <t>-4,06; 132,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>184,97; 519,28</t>
+          <t>228,66; 601,14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>1,59</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,48</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,44</t>
+          <t>2,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,51</t>
+          <t>-0,95; 2,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,9</t>
+          <t>-1,34; 0,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,76</t>
+          <t>0,36; 2,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,41</t>
+          <t>0,46; 3,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,91</t>
+          <t>0,15; 2,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,77</t>
+          <t>2,43; 4,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,26</t>
+          <t>0,1; 2,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,39</t>
+          <t>-0,21; 1,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,29</t>
+          <t>1,65; 3,51</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166,89%</t>
+          <t>184,38%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1473,06%</t>
+          <t>1523,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>427,4%</t>
+          <t>451,58%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 726,7</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 322,02</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7,99; 858,93</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 426,62</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-3,42; 927,88</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 718,4</t>
+          <t>-7,76; 804,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 492,0</t>
+          <t>-37,31; 478,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>142,51; 1271,15</t>
+          <t>136,99; 1371,33</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,06</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,44</t>
+          <t>6,97</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>5,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,97</t>
+          <t>-0,31; 1,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,83</t>
+          <t>-0,41; 0,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,87</t>
+          <t>2,49; 4,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,39</t>
+          <t>1,51; 3,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,6</t>
+          <t>0,84; 2,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,77; 7,55</t>
+          <t>6,0; 7,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,01</t>
+          <t>0,81; 1,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,52</t>
+          <t>0,43; 1,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,56</t>
+          <t>4,57; 5,76</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>206,9%</t>
+          <t>221,82%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>250,19%</t>
+          <t>271,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>236,14%</t>
+          <t>255,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 82,12</t>
+          <t>-17,29; 87,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 66,07</t>
+          <t>-24,6; 65,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>115,26; 338,48</t>
+          <t>129,99; 329,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52,66; 155,61</t>
+          <t>49,74; 151,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,04; 114,59</t>
+          <t>28,17; 120,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>171,73; 346,77</t>
+          <t>192,66; 358,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,82; 107,57</t>
+          <t>36,8; 112,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,39; 86,25</t>
+          <t>18,77; 83,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>172,95; 309,21</t>
+          <t>193,7; 326,05</t>
         </is>
       </c>
     </row>
